--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/TEXAS_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/TEXAS_2019.xlsx
@@ -1309,7 +1309,7 @@
         <v>16</v>
       </c>
       <c r="D53">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="54">
@@ -2029,7 +2029,7 @@
         <v>16</v>
       </c>
       <c r="D93">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="94">
@@ -2785,7 +2785,7 @@
         <v>16</v>
       </c>
       <c r="D135">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="136">
@@ -2983,7 +2983,7 @@
         <v>16</v>
       </c>
       <c r="D146">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="147">
@@ -3055,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="D150">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="151">
@@ -3109,7 +3109,7 @@
         <v>165</v>
       </c>
       <c r="D153">
-        <v>0.0009488866396761133</v>
+        <v>0.0009488866396761132</v>
       </c>
     </row>
     <row r="154">
@@ -3829,7 +3829,7 @@
         <v>16</v>
       </c>
       <c r="D193">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="194">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C196">
@@ -4081,7 +4081,7 @@
         <v>1643</v>
       </c>
       <c r="D207">
-        <v>0.009448610599926389</v>
+        <v>0.009448610599926388</v>
       </c>
     </row>
     <row r="208">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C261">
@@ -5647,7 +5647,7 @@
         <v>16</v>
       </c>
       <c r="D294">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="295">
@@ -6439,7 +6439,7 @@
         <v>16</v>
       </c>
       <c r="D338">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="339">
@@ -7663,7 +7663,7 @@
         <v>16</v>
       </c>
       <c r="D406">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="407">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C421">
@@ -8239,7 +8239,7 @@
         <v>1578</v>
       </c>
       <c r="D438">
-        <v>0.009074806772175193</v>
+        <v>0.009074806772175191</v>
       </c>
     </row>
     <row r="439">
@@ -8293,7 +8293,7 @@
         <v>1721</v>
       </c>
       <c r="D441">
-        <v>0.009897175193227825</v>
+        <v>0.009897175193227824</v>
       </c>
     </row>
     <row r="442">
@@ -9607,7 +9607,7 @@
         <v>164</v>
       </c>
       <c r="D514">
-        <v>0.0009431358115568641</v>
+        <v>0.000943135811556864</v>
       </c>
     </row>
     <row r="515">
@@ -10309,7 +10309,7 @@
         <v>16</v>
       </c>
       <c r="D553">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="554">
@@ -10651,7 +10651,7 @@
         <v>16</v>
       </c>
       <c r="D572">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="573">
@@ -10813,7 +10813,7 @@
         <v>16</v>
       </c>
       <c r="D581">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="582">
@@ -11461,7 +11461,7 @@
         <v>16</v>
       </c>
       <c r="D617">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="618">
@@ -12181,7 +12181,7 @@
         <v>16</v>
       </c>
       <c r="D657">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="658">
@@ -12343,7 +12343,7 @@
         <v>16</v>
       </c>
       <c r="D666">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="667">
@@ -13009,7 +13009,7 @@
         <v>167</v>
       </c>
       <c r="D703">
-        <v>0.0009603882959146117</v>
+        <v>0.0009603882959146116</v>
       </c>
     </row>
     <row r="704">
@@ -13387,7 +13387,7 @@
         <v>16</v>
       </c>
       <c r="D724">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="725">
@@ -16015,7 +16015,7 @@
         <v>16</v>
       </c>
       <c r="D870">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="871">
@@ -16872,14 +16872,14 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C918">
         <v>16</v>
       </c>
       <c r="D918">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="919">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C920">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C921">
@@ -16951,7 +16951,7 @@
         <v>16</v>
       </c>
       <c r="D922">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="923">
@@ -17329,7 +17329,7 @@
         <v>16</v>
       </c>
       <c r="D943">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="944">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1082">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1083">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1141">
@@ -20904,7 +20904,7 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1142">
@@ -23359,7 +23359,7 @@
         <v>16</v>
       </c>
       <c r="D1278">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1279">
@@ -24331,7 +24331,7 @@
         <v>16</v>
       </c>
       <c r="D1332">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1333">
@@ -24727,7 +24727,7 @@
         <v>167</v>
       </c>
       <c r="D1354">
-        <v>0.0009603882959146117</v>
+        <v>0.0009603882959146116</v>
       </c>
     </row>
     <row r="1355">
@@ -27301,7 +27301,7 @@
         <v>164</v>
       </c>
       <c r="D1497">
-        <v>0.0009431358115568641</v>
+        <v>0.000943135811556864</v>
       </c>
     </row>
     <row r="1498">
@@ -27589,7 +27589,7 @@
         <v>16</v>
       </c>
       <c r="D1513">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1514">
@@ -28471,7 +28471,7 @@
         <v>16</v>
       </c>
       <c r="D1562">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1563">
@@ -29983,7 +29983,7 @@
         <v>16</v>
       </c>
       <c r="D1646">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1647">
@@ -30991,7 +30991,7 @@
         <v>16</v>
       </c>
       <c r="D1702">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1703">
@@ -31056,7 +31056,7 @@
       </c>
       <c r="B1706" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1706">
@@ -32107,7 +32107,7 @@
         <v>16</v>
       </c>
       <c r="D1764">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1765">
@@ -33439,7 +33439,7 @@
         <v>16</v>
       </c>
       <c r="D1838">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1839">
@@ -33493,7 +33493,7 @@
         <v>16</v>
       </c>
       <c r="D1841">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1842">
@@ -34681,7 +34681,7 @@
         <v>16</v>
       </c>
       <c r="D1907">
-        <v>9.201324990798675E-05</v>
+        <v>9.201324990798676E-05</v>
       </c>
     </row>
     <row r="1908">
@@ -36247,7 +36247,7 @@
         <v>160</v>
       </c>
       <c r="D1994">
-        <v>0.0009201324990798675</v>
+        <v>0.0009201324990798676</v>
       </c>
     </row>
     <row r="1995">
